--- a/education_surveys/017_music_ear_training_survey--education_surveys.xlsx
+++ b/education_surveys/017_music_ear_training_survey--education_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1156,7 +1156,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ear_training</t>
+          <t>ear training</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>music_theory</t>
+          <t>music theory</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>aural_skills</t>
+          <t>aural skills</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>sight_reading</t>
+          <t>sight reading</t>
         </is>
       </c>
     </row>
@@ -1241,7 +1241,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ear_training_workout</t>
+          <t>ear training workout</t>
         </is>
       </c>
     </row>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>music_video_game</t>
+          <t>music video game</t>
         </is>
       </c>
     </row>
@@ -1309,7 +1309,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>no_methods</t>
+          <t>no methods</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>music_theory_1</t>
+          <t>music theory 1</t>
         </is>
       </c>
     </row>
@@ -1343,7 +1343,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>music_theory_2</t>
+          <t>music theory 2</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>music_theory_3</t>
+          <t>music theory 3</t>
         </is>
       </c>
     </row>
@@ -1377,7 +1377,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>no_music_theory</t>
+          <t>no music theory</t>
         </is>
       </c>
     </row>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>aural_skills_1</t>
+          <t>aural skills 1</t>
         </is>
       </c>
     </row>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>aural_skills_2</t>
+          <t>aural skills 2</t>
         </is>
       </c>
     </row>
@@ -1445,7 +1445,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>app_1</t>
+          <t>app 1</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>app_2</t>
+          <t>app 2</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>no_app_ideas</t>
+          <t>no app ideas</t>
         </is>
       </c>
     </row>
